--- a/astro-site/public/dl/bar-checklist-templates/BONUS-01-bar-pre-shift-meeting-template.xlsx
+++ b/astro-site/public/dl/bar-checklist-templates/BONUS-01-bar-pre-shift-meeting-template.xlsx
@@ -1062,7 +1062,7 @@
       </c>
       <c r="B9" s="32" t="inlineStr">
         <is>
-          <t>Active promotions (happy hour, 2-for-1, etc.)</t>
+          <t>Active promotions (happy hour, drink of the day, food specials), only as your state allows: some ban 2-for-1s and drink discounts</t>
         </is>
       </c>
       <c r="C9" s="33" t="inlineStr">
